--- a/data/trans_dic/IP16A01-Edad-trans_dic.xlsx
+++ b/data/trans_dic/IP16A01-Edad-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -526,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que consumiero medicamentos para  el catarro, gripe, garganta, bronquios</t>
+          <t>Menores que consumiero medicamentos para  el catarro, gripe, garganta, bronquios (tasa de respuesta: 99,94%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -716,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>95,93; 100</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>59,6; 83,3</t>
+          <t>62,26; 84,32</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>48,3; 75,43</t>
+          <t>46,93; 75,51</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>41,17; 79,86</t>
+          <t>42,94; 78,86</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>95,75; 100</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>57,53; 82,2</t>
+          <t>56,42; 80,45</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>51,96; 83,67</t>
+          <t>54,17; 83,47</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>53,52; 83,14</t>
+          <t>53,51; 84,23</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>97,89; 100</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>62,78; 79,74</t>
+          <t>62,47; 79,07</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>55,85; 76,16</t>
+          <t>54,8; 75,7</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>54,73; 77,87</t>
+          <t>54,63; 78,21</t>
         </is>
       </c>
     </row>
@@ -856,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>97,14; 100</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>57,69; 78,69</t>
+          <t>58,56; 79,27</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>55,52; 78,43</t>
+          <t>54,37; 77,04</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>33,43; 59,6</t>
+          <t>33,06; 57,75</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>97,51; 100</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>62,99; 81,31</t>
+          <t>63,72; 81,6</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>51,01; 74,11</t>
+          <t>51,16; 74,94</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>50,54; 73,24</t>
+          <t>49,82; 74,55</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>98,66; 100</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>64,47; 77,66</t>
+          <t>64,04; 78,08</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>56,27; 72,9</t>
+          <t>55,63; 73,29</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>45,81; 63,46</t>
+          <t>46,31; 64,56</t>
         </is>
       </c>
     </row>
@@ -996,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>94,39; 100</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>35,28; 66,75</t>
+          <t>35,01; 66,24</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>50,89; 77,95</t>
+          <t>51,18; 77,16</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>39,08; 66,12</t>
+          <t>38,28; 65,84</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>94,84; 100</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>32,59; 64,05</t>
+          <t>32,15; 66,0</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>26,29; 53,96</t>
+          <t>25,1; 52,6</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>44,89; 70,45</t>
+          <t>45,3; 71,89</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>97,26; 100</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>40,0; 62,51</t>
+          <t>39,33; 60,39</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>43,22; 62,56</t>
+          <t>42,65; 61,85</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>45,69; 65,04</t>
+          <t>46,29; 66,11</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>95,84; 100</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>54,26; 83,18</t>
+          <t>54,89; 83,09</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>25,06; 60,93</t>
+          <t>26,23; 60,73</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>44,81; 88,81</t>
+          <t>44,71; 88,72</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>96,81; 100</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>23,81; 55,48</t>
+          <t>23,77; 53,78</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>30,23; 66,34</t>
+          <t>31,54; 64,85</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>39,33; 64,66</t>
+          <t>39,28; 64,47</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>98,17; 100</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>43,74; 67,61</t>
+          <t>43,98; 66,8</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>31,86; 58,37</t>
+          <t>32,85; 57,7</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>47,32; 78,62</t>
+          <t>47,14; 78,36</t>
         </is>
       </c>
     </row>
@@ -1276,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>99,0; 100</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>60,7; 73,37</t>
+          <t>60,42; 72,9</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>53,45; 68,0</t>
+          <t>54,28; 68,45</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>48,7; 76,03</t>
+          <t>47,96; 74,88</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>99,11; 100</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>55,88; 68,32</t>
+          <t>56,39; 68,87</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>47,55; 62,83</t>
+          <t>47,95; 62,67</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>53,0; 66,52</t>
+          <t>51,99; 65,84</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>99,53; 100</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>60,41; 69,13</t>
+          <t>60,25; 69,2</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>53,08; 63,13</t>
+          <t>53,5; 63,19</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>52,86; 68,42</t>
+          <t>52,52; 67,87</t>
         </is>
       </c>
     </row>
@@ -1356,4 +1357,1204 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N19"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que consumiero medicamentos para  el catarro, gripe, garganta, bronquios (tasa de respuesta: 99,94%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="n"/>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="n"/>
+      <c r="J1" s="3" t="n"/>
+      <c r="K1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="L1" s="3" t="n"/>
+      <c r="M1" s="3" t="n"/>
+      <c r="N1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="L2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="M2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="N2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+      <c r="L3" s="2" t="n"/>
+      <c r="M3" s="2" t="n"/>
+      <c r="N3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>0-2</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>77</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>29035</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>26913</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>16913</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>10216</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>29655</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>26654</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>16757</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>15583</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>58690</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>53567</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>33669</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>25799</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>22723; 30772</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>12685; 20414</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>6863; 12604</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>21678; 30913</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>12989; 20013</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>11963; 18832</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>46807; 59239</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>27953; 38612</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>20944; 29986</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>3-7</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>76</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>142</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>121</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>85</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>83</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>43221</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>37673</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>28359</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>21575</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>50960</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>48988</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>27241</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>30960</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>94181</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>86660</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>55599</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>52535</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>31721; 42935</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>22965; 32539</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>15415; 26926</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>42927; 54971</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>22050; 32295</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>24404; 36518</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>77827; 94887</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>47468; 62544</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>44275; 61726</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>8-11</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>69</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>22507</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>14839</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>23607</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>19585</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>23866</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>13746</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>12961</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>26988</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>46373</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>28585</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>36567</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>46573</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>10141; 19186</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>18488; 27873</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>14220; 24459</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>8974; 18424</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>8396; 17593</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>20913; 33193</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>22374; 34352</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>29674; 43026</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>38565; 55085</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>12-15</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>104</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>85</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>30543</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>19261</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>9334</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>52641</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>39438</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>9559</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>11021</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>34032</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>69981</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>28821</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>20356</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>86672</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>14914; 22575</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>5788; 13400</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>34857; 69165</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>5910; 13374</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>7178; 14759</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>25410; 41707</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>22884; 34763</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>14726; 25862</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>67242; 111785</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>190</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>141</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>119</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>125</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>215</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>138</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>155</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>405</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>279</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>219</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>280</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>125305</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>98686</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>78212</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>104018</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>143919</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>98947</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>67979</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>107562</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>269224</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>197633</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>146191</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>211579</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>88690; 107012</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>69181; 87247</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>85233; 133075</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>89414; 109213</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>59106; 77262</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>94726; 119965</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>183996; 211302</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>134154; 158441</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>189045; 244269</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="9">
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="C1:F1"/>
+    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP16A01-Edad-trans_dic.xlsx
+++ b/data/trans_dic/IP16A01-Edad-trans_dic.xlsx
@@ -722,17 +722,17 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>62,26; 84,32</t>
+          <t>60,72; 83,64</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>46,93; 75,51</t>
+          <t>47,63; 75,67</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>42,94; 78,86</t>
+          <t>44,15; 81,36</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -742,17 +742,17 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>56,42; 80,45</t>
+          <t>53,58; 80,32</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>54,17; 83,47</t>
+          <t>54,04; 82,3</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>53,51; 84,23</t>
+          <t>52,8; 83,11</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -762,17 +762,17 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>62,47; 79,07</t>
+          <t>62,41; 79,72</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>54,8; 75,7</t>
+          <t>55,05; 76,86</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>54,63; 78,21</t>
+          <t>54,04; 78,14</t>
         </is>
       </c>
     </row>
@@ -862,17 +862,17 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>58,56; 79,27</t>
+          <t>58,66; 78,86</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>54,37; 77,04</t>
+          <t>55,45; 78,3</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>33,06; 57,75</t>
+          <t>33,3; 58,82</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -882,17 +882,17 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>63,72; 81,6</t>
+          <t>64,36; 81,52</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>51,16; 74,94</t>
+          <t>49,62; 74,23</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>49,82; 74,55</t>
+          <t>51,41; 74,58</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -902,17 +902,17 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>64,04; 78,08</t>
+          <t>64,0; 77,6</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>55,63; 73,29</t>
+          <t>56,26; 73,48</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>46,31; 64,56</t>
+          <t>44,68; 62,98</t>
         </is>
       </c>
     </row>
@@ -1002,17 +1002,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>35,01; 66,24</t>
+          <t>35,37; 64,83</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>51,18; 77,16</t>
+          <t>51,15; 77,55</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>38,28; 65,84</t>
+          <t>39,4; 66,27</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1022,17 +1022,17 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>32,15; 66,0</t>
+          <t>33,77; 65,05</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>25,1; 52,6</t>
+          <t>24,97; 53,59</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>45,3; 71,89</t>
+          <t>44,18; 71,78</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
@@ -1042,17 +1042,17 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>39,33; 60,39</t>
+          <t>39,9; 61,35</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>42,65; 61,85</t>
+          <t>42,22; 62,1</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>46,29; 66,11</t>
+          <t>44,8; 64,51</t>
         </is>
       </c>
     </row>
@@ -1142,17 +1142,17 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>54,89; 83,09</t>
+          <t>55,3; 83,31</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>26,23; 60,73</t>
+          <t>25,6; 60,45</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>44,71; 88,72</t>
+          <t>44,36; 89,67</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1162,17 +1162,17 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>23,77; 53,78</t>
+          <t>23,91; 57,36</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>31,54; 64,85</t>
+          <t>31,38; 67,26</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>39,28; 64,47</t>
+          <t>39,55; 65,8</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1182,17 +1182,17 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>43,98; 66,8</t>
+          <t>43,14; 66,42</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>32,85; 57,7</t>
+          <t>32,79; 57,9</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>47,14; 78,36</t>
+          <t>47,92; 79,29</t>
         </is>
       </c>
     </row>
@@ -1282,17 +1282,17 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>60,42; 72,9</t>
+          <t>61,17; 73,9</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>54,28; 68,45</t>
+          <t>53,74; 68,17</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>47,96; 74,88</t>
+          <t>48,28; 74,25</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1302,17 +1302,17 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>56,39; 68,87</t>
+          <t>56,07; 69,1</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>47,95; 62,67</t>
+          <t>47,78; 62,35</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>51,99; 65,84</t>
+          <t>52,18; 65,89</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -1322,17 +1322,17 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>60,25; 69,2</t>
+          <t>59,66; 69,02</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>53,5; 63,19</t>
+          <t>52,85; 62,89</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>52,52; 67,87</t>
+          <t>53,2; 67,73</t>
         </is>
       </c>
     </row>
@@ -1650,17 +1650,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>22723; 30772</t>
+          <t>22161; 30528</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>12685; 20414</t>
+          <t>12876; 20455</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>6863; 12604</t>
+          <t>7057; 13004</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -1670,17 +1670,17 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>21678; 30913</t>
+          <t>20589; 30864</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>12989; 20013</t>
+          <t>12956; 19731</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>11963; 18832</t>
+          <t>11805; 18581</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -1690,17 +1690,17 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>46807; 59239</t>
+          <t>46761; 59731</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>27953; 38612</t>
+          <t>28078; 39203</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>20944; 29986</t>
+          <t>20719; 29961</t>
         </is>
       </c>
     </row>
@@ -1858,17 +1858,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>31721; 42935</t>
+          <t>31774; 42713</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>22965; 32539</t>
+          <t>23423; 33074</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>15415; 26926</t>
+          <t>15524; 27423</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1878,17 +1878,17 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>42927; 54971</t>
+          <t>43353; 54919</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>22050; 32295</t>
+          <t>21383; 31990</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>24404; 36518</t>
+          <t>25180; 36533</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
@@ -1898,17 +1898,17 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>77827; 94887</t>
+          <t>77784; 94301</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>47468; 62544</t>
+          <t>48006; 62706</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>44275; 61726</t>
+          <t>42713; 60214</t>
         </is>
       </c>
     </row>
@@ -2066,17 +2066,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>10141; 19186</t>
+          <t>10246; 18780</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>18488; 27873</t>
+          <t>18477; 28015</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>14220; 24459</t>
+          <t>14637; 24618</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -2086,17 +2086,17 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>8974; 18424</t>
+          <t>9428; 18160</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>8396; 17593</t>
+          <t>8352; 17925</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>20913; 33193</t>
+          <t>20398; 33139</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -2106,17 +2106,17 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>22374; 34352</t>
+          <t>22695; 34898</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>29674; 43026</t>
+          <t>29374; 43203</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>38565; 55085</t>
+          <t>37323; 53753</t>
         </is>
       </c>
     </row>
@@ -2274,17 +2274,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>14914; 22575</t>
+          <t>15024; 22634</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>5788; 13400</t>
+          <t>5649; 13338</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>34857; 69165</t>
+          <t>34583; 69904</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2294,17 +2294,17 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>5910; 13374</t>
+          <t>5946; 14264</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>7178; 14759</t>
+          <t>7140; 15307</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>25410; 41707</t>
+          <t>25588; 42567</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
@@ -2314,17 +2314,17 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>22884; 34763</t>
+          <t>22451; 34564</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>14726; 25862</t>
+          <t>14696; 25952</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>67242; 111785</t>
+          <t>68356; 113111</t>
         </is>
       </c>
     </row>
@@ -2482,17 +2482,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>88690; 107012</t>
+          <t>89801; 108483</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>69181; 87247</t>
+          <t>68501; 86885</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>85233; 133075</t>
+          <t>85806; 131950</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2502,17 +2502,17 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>89414; 109213</t>
+          <t>88910; 109578</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>59106; 77262</t>
+          <t>58903; 76857</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>94726; 119965</t>
+          <t>95069; 120047</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -2522,17 +2522,17 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>183996; 211302</t>
+          <t>182190; 210777</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>134154; 158441</t>
+          <t>132523; 157678</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>189045; 244269</t>
+          <t>191488; 243782</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP16A01-Edad-trans_dic.xlsx
+++ b/data/trans_dic/IP16A01-Edad-trans_dic.xlsx
@@ -527,13 +527,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que consumiero medicamentos para  el catarro, gripe, garganta, bronquios (tasa de respuesta: 99,94%)</t>
+          <t>Menores que consumieron medicamentos para  el catarro, gripe, garganta, bronquios (tasa de respuesta: 99,94%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -541,7 +541,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -654,44 +654,44 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
+          <t>69,36%</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>69,89%</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>71,53%</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
           <t>73,74%</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>62,56%</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>63,92%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>62,84%</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>69,36%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>69,89%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>69,7%</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
           <t>71,5%</t>
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>67,29%</t>
+          <t>67,64%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>60,72; 83,64</t>
+          <t>57,53; 82,2</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>47,63; 75,67</t>
+          <t>51,96; 83,67</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>44,15; 81,36</t>
+          <t>56,27; 83,99</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -742,17 +742,17 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>53,58; 80,32</t>
+          <t>59,6; 83,3</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>54,04; 82,3</t>
+          <t>48,3; 75,43</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>52,8; 83,11</t>
+          <t>40,34; 79,54</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -762,17 +762,17 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>62,41; 79,72</t>
+          <t>62,78; 79,74</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>55,05; 76,86</t>
+          <t>55,85; 76,16</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>54,04; 78,14</t>
+          <t>54,69; 78,03</t>
         </is>
       </c>
     </row>
@@ -794,44 +794,44 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
+          <t>72,72%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>63,21%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>66,08%</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
           <t>69,55%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>67,14%</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>46,28%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>49,03%</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>72,72%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>63,21%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>63,2%</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
           <t>71,31%</t>
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>54,95%</t>
+          <t>57,59%</t>
         </is>
       </c>
     </row>
@@ -862,17 +862,17 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>58,66; 78,86</t>
+          <t>62,99; 81,31</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>55,45; 78,3</t>
+          <t>51,01; 74,11</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>33,3; 58,82</t>
+          <t>54,34; 75,77</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -882,17 +882,17 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>64,36; 81,52</t>
+          <t>57,69; 78,69</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>49,62; 74,23</t>
+          <t>55,52; 78,43</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>51,41; 74,58</t>
+          <t>37,26; 61,33</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -902,17 +902,17 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>64,0; 77,6</t>
+          <t>64,47; 77,66</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>56,26; 73,48</t>
+          <t>56,27; 72,9</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>44,68; 62,98</t>
+          <t>48,64; 65,36</t>
         </is>
       </c>
     </row>
@@ -934,44 +934,44 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
+          <t>49,24%</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>38,75%</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>59,26%</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
           <t>51,23%</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>65,35%</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>52,72%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>52,35%</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>49,24%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>38,75%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>58,45%</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
           <t>50,25%</t>
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>55,9%</t>
+          <t>56,06%</t>
         </is>
       </c>
     </row>
@@ -1002,17 +1002,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>35,37; 64,83</t>
+          <t>32,59; 64,05</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>51,15; 77,55</t>
+          <t>26,29; 53,96</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>39,4; 66,27</t>
+          <t>45,79; 71,87</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1022,17 +1022,17 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>33,77; 65,05</t>
+          <t>35,28; 66,75</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>24,97; 53,59</t>
+          <t>50,89; 77,95</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>44,18; 71,78</t>
+          <t>38,86; 65,81</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
@@ -1042,17 +1042,17 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>39,9; 61,35</t>
+          <t>40,0; 62,51</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>42,22; 62,1</t>
+          <t>43,22; 62,56</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>44,8; 64,51</t>
+          <t>45,85; 65,23</t>
         </is>
       </c>
     </row>
@@ -1074,44 +1074,44 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
+          <t>38,44%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>48,43%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>51,97%</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
           <t>70,89%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>42,3%</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>67,53%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>58,34%</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>38,44%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>48,43%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>52,61%</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
           <t>55,39%</t>
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>60,76%</t>
+          <t>54,8%</t>
         </is>
       </c>
     </row>
@@ -1142,17 +1142,17 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>55,3; 83,31</t>
+          <t>23,81; 55,48</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>25,6; 60,45</t>
+          <t>30,23; 66,34</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>44,36; 89,67</t>
+          <t>38,76; 64,58</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1162,17 +1162,17 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>23,91; 57,36</t>
+          <t>54,26; 83,18</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>31,38; 67,26</t>
+          <t>25,06; 60,93</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>39,55; 65,8</t>
+          <t>44,83; 69,4</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1182,17 +1182,17 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>43,14; 66,42</t>
+          <t>43,74; 67,61</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>32,79; 57,9</t>
+          <t>31,86; 58,37</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>47,92; 79,29</t>
+          <t>45,47; 64,36</t>
         </is>
       </c>
     </row>
@@ -1214,44 +1214,44 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
+          <t>62,4%</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>55,14%</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>59,51%</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
           <t>67,23%</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="I12" s="2" t="inlineStr">
         <is>
           <t>61,36%</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>58,53%</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>54,53%</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>62,4%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>55,14%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>59,03%</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
           <t>64,72%</t>
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>58,79%</t>
+          <t>57,2%</t>
         </is>
       </c>
     </row>
@@ -1282,17 +1282,17 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>61,17; 73,9</t>
+          <t>55,88; 68,32</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>53,74; 68,17</t>
+          <t>47,55; 62,83</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>48,28; 74,25</t>
+          <t>53,33; 66,89</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1302,17 +1302,17 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>56,07; 69,1</t>
+          <t>60,7; 73,37</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>47,78; 62,35</t>
+          <t>53,45; 68,0</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>52,18; 65,89</t>
+          <t>47,2; 61,09</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -1322,17 +1322,17 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>59,66; 69,02</t>
+          <t>60,41; 69,13</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>52,85; 62,89</t>
+          <t>53,08; 63,13</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>53,2; 67,73</t>
+          <t>52,4; 61,93</t>
         </is>
       </c>
     </row>
@@ -1387,13 +1387,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que consumiero medicamentos para  el catarro, gripe, garganta, bronquios (tasa de respuesta: 99,94%)</t>
+          <t>Menores que consumieron medicamentos para  el catarro, gripe, garganta, bronquios (tasa de respuesta: 99,94%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -1401,7 +1401,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -1509,42 +1509,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>46</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>40</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>27</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>20</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>44</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>30</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -1577,42 +1577,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>29655</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>26654</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>16757</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>12471</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
           <t>29035</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>26913</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="I5" s="2" t="inlineStr">
         <is>
           <t>16913</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>10216</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>29655</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>26654</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>16757</t>
-        </is>
-      </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>15583</t>
+          <t>8904</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1632,7 +1632,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>25799</t>
+          <t>21374</t>
         </is>
       </c>
     </row>
@@ -1650,17 +1650,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>22161; 30528</t>
+          <t>22108; 31587</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>12876; 20455</t>
+          <t>12457; 20062</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>7057; 13004</t>
+          <t>9810; 14642</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -1670,17 +1670,17 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>20589; 30864</t>
+          <t>21752; 30403</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>12956; 19731</t>
+          <t>13057; 20392</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>11805; 18581</t>
+          <t>5716; 11270</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -1690,17 +1690,17 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>46761; 59731</t>
+          <t>47037; 59746</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>28078; 39203</t>
+          <t>28487; 38850</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>20719; 29961</t>
+          <t>17284; 24659</t>
         </is>
       </c>
     </row>
@@ -1717,42 +1717,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>76</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
           <t>66</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>53</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="I7" s="2" t="inlineStr">
         <is>
           <t>45</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="J7" s="2" t="inlineStr">
         <is>
           <t>36</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>76</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>68</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>47</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -1785,42 +1785,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>50960</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>48988</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>27241</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>27248</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>43221</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>37673</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>28359</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>21575</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>50960</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>48988</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>27241</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>30960</t>
+          <t>20052</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1840,7 +1840,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>52535</t>
+          <t>47300</t>
         </is>
       </c>
     </row>
@@ -1858,17 +1858,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>31774; 42713</t>
+          <t>42432; 54771</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>23423; 33074</t>
+          <t>21981; 31937</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>15524; 27423</t>
+          <t>22409; 31244</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1878,17 +1878,17 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>43353; 54919</t>
+          <t>31250; 42621</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>21383; 31990</t>
+          <t>23451; 33129</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>25180; 36533</t>
+          <t>15238; 25082</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
@@ -1898,17 +1898,17 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>77784; 94301</t>
+          <t>78354; 94383</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>48006; 62706</t>
+          <t>48017; 62205</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>42713; 60214</t>
+          <t>39953; 53682</t>
         </is>
       </c>
     </row>
@@ -1925,42 +1925,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>33</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>21</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>34</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="J10" s="2" t="inlineStr">
         <is>
           <t>29</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>33</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1993,42 +1993,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>23866</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>13746</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>12961</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>26058</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
           <t>22507</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>14839</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="I11" s="2" t="inlineStr">
         <is>
           <t>23607</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>19585</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>23866</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>13746</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>12961</t>
-        </is>
-      </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>26988</t>
+          <t>19866</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2048,7 +2048,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>46573</t>
+          <t>45924</t>
         </is>
       </c>
     </row>
@@ -2066,17 +2066,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>10246; 18780</t>
+          <t>9098; 17878</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>18477; 28015</t>
+          <t>8794; 18048</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>14637; 24618</t>
+          <t>20135; 31603</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -2086,17 +2086,17 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>9428; 18160</t>
+          <t>10219; 19335</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>8352; 17925</t>
+          <t>18383; 28159</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>20398; 33139</t>
+          <t>14746; 24974</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -2106,17 +2106,17 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>22695; 34898</t>
+          <t>22753; 35557</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>29374; 43203</t>
+          <t>30068; 43521</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>37323; 53753</t>
+          <t>37561; 53438</t>
         </is>
       </c>
     </row>
@@ -2133,42 +2133,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
           <t>45</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>27</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="I13" s="2" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="J13" s="2" t="inlineStr">
         <is>
           <t>40</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>59</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>45</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -2201,42 +2201,42 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>39438</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>9559</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>11021</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>32386</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
           <t>30543</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>19261</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>9334</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>52641</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>39438</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>9559</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>11021</t>
-        </is>
-      </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>34032</t>
+          <t>29156</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2256,7 +2256,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>86672</t>
+          <t>61542</t>
         </is>
       </c>
     </row>
@@ -2274,17 +2274,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>15024; 22634</t>
+          <t>5922; 13796</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>5649; 13338</t>
+          <t>6879; 15097</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>34583; 69904</t>
+          <t>24151; 40242</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2294,17 +2294,17 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>5946; 14264</t>
+          <t>14741; 22599</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>7140; 15307</t>
+          <t>5529; 13444</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>25588; 42567</t>
+          <t>22407; 34685</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
@@ -2314,17 +2314,17 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>22451; 34564</t>
+          <t>22762; 35180</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>14696; 25952</t>
+          <t>14283; 26162</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>68356; 113111</t>
+          <t>51064; 72277</t>
         </is>
       </c>
     </row>
@@ -2341,42 +2341,42 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>215</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>138</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>155</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
           <t>190</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>141</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="I16" s="2" t="inlineStr">
         <is>
           <t>119</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="J16" s="2" t="inlineStr">
         <is>
           <t>125</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>215</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>138</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>155</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -2409,42 +2409,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>143919</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>98947</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>67979</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>98162</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
           <t>125305</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>98686</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="I17" s="2" t="inlineStr">
         <is>
           <t>78212</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>104018</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>143919</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>98947</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>67979</t>
-        </is>
-      </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>107562</t>
+          <t>77978</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2464,7 +2464,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>211579</t>
+          <t>176140</t>
         </is>
       </c>
     </row>
@@ -2482,17 +2482,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>89801; 108483</t>
+          <t>88618; 108340</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>68501; 86885</t>
+          <t>58624; 77455</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>85806; 131950</t>
+          <t>87974; 110339</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2502,17 +2502,17 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>88910; 109578</t>
+          <t>89108; 107709</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>58903; 76857</t>
+          <t>68124; 86669</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>95069; 120047</t>
+          <t>67490; 87349</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -2522,17 +2522,17 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>182190; 210777</t>
+          <t>184488; 211108</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>132523; 157678</t>
+          <t>133087; 158295</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>191488; 243782</t>
+          <t>161358; 190697</t>
         </is>
       </c>
     </row>
